--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JH\code\badmintonAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329EA2D0-AA3B-4831-8099-95C86A9BB740}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE26F1-E3D0-4A90-B7D7-14DDAE2122C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="重大赛事" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="170">
   <si>
     <t>年份</t>
   </si>
@@ -478,6 +478,90 @@
   </si>
   <si>
     <t>下载</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷兰青少年精英赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dutch Junior U19 International</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>荷兰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8进4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>尤伯杯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Uber Cup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>董天尧个人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩国大师赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决赛 朱轩辰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Korea Master</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super 300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Super 1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩国</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石宇奇 vs 桃田贤斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛事整理16场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞士公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛事整理19场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>林丹 vs 李宗伟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2004 - 2018赛事整理40场</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -485,7 +569,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -514,6 +598,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -535,7 +626,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -544,6 +635,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1265,10 +1359,10 @@
       <c r="B14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="C14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E14" s="2">
@@ -1329,10 +1423,10 @@
       <c r="B16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="C16" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E16" s="2">
@@ -1361,10 +1455,10 @@
       <c r="B17" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E17" s="2">
@@ -1425,7 +1519,7 @@
       <c r="B19" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D19" s="3" t="s">
@@ -1460,7 +1554,7 @@
       <c r="C20" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E20" s="2">
@@ -1553,7 +1647,7 @@
       <c r="B23" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C23" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D23" s="3" t="s">
@@ -1649,10 +1743,10 @@
       <c r="B26" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E26" s="2">
@@ -1844,7 +1938,7 @@
       <c r="C32" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="D32" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E32" s="2">
@@ -1908,7 +2002,7 @@
       <c r="C34" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E34" s="2">
@@ -1937,7 +2031,7 @@
       <c r="B35" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -4655,128 +4749,231 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4629F87-AE32-4135-AEE0-F396104DC0E9}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:A119"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="4" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="6" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="7" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="9" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="10" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="11" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="12" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="13" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="14" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="15" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="16" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="17" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="18" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="19" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="20" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="21" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="22" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="23" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="24" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="25" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="26" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="27" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="28" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="29" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="30" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="31" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="32" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D4" s="2">
+        <v>46175</v>
+      </c>
+      <c r="E4" s="2">
+        <v>46180</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="D6" s="2">
+        <v>46182</v>
+      </c>
+      <c r="E6" s="2">
+        <v>46187</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D8" s="2">
+        <v>45923</v>
+      </c>
+      <c r="E8" s="2">
+        <v>45928</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B9" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JH\code\badmintonAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE26F1-E3D0-4A90-B7D7-14DDAE2122C3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721CBB19-EA23-4CB1-BFD9-A194E15DCE99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="重大赛事" sheetId="1" r:id="rId1"/>
@@ -4743,6 +4743,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JH\code\badmintonAI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{721CBB19-EA23-4CB1-BFD9-A194E15DCE99}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E81327-9C26-47A3-92C2-0EA0906ECB11}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="193">
   <si>
     <t>年份</t>
   </si>
@@ -562,6 +562,98 @@
   </si>
   <si>
     <t>2004 - 2018赛事整理40场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他赛事整理179场</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8进4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>新加坡公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丹麦公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>香港公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰国公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>印尼大师赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8进4等</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>海露公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>加拿大公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>决赛 半决赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>澳大利亚公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美国公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰国大师赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>赛德莫迪国际赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瑞士公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥尔良大师赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>澳门公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>韩国大师赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>德国公开赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>年终总决赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>小组赛</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1711,10 +1803,10 @@
       <c r="B25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C25" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E25" s="2">
@@ -1775,10 +1867,10 @@
       <c r="B27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D27" s="3" t="s">
+      <c r="C27" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E27" s="2">
@@ -1807,10 +1899,10 @@
       <c r="B28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D28" s="3" t="s">
+      <c r="C28" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E28" s="2">
@@ -1839,10 +1931,10 @@
       <c r="B29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="3" t="s">
+      <c r="C29" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E29" s="2">
@@ -1871,10 +1963,10 @@
       <c r="B30" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E30" s="2">
@@ -1935,7 +2027,7 @@
       <c r="B32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C32" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D32" s="4" t="s">
@@ -1967,10 +2059,10 @@
       <c r="B33" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D33" s="3" t="s">
+      <c r="C33" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E33" s="2">
@@ -1999,7 +2091,7 @@
       <c r="B34" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="4" t="s">
         <v>148</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -2034,7 +2126,7 @@
       <c r="C35" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D35" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E35" s="2">
@@ -2127,10 +2219,10 @@
       <c r="B38" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D38" s="3" t="s">
+      <c r="C38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E38" s="2">
@@ -2159,10 +2251,10 @@
       <c r="B39" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D39" s="3" t="s">
+      <c r="C39" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E39" s="2">
@@ -2223,10 +2315,10 @@
       <c r="B41" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C41" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="3" t="s">
+      <c r="C41" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E41" s="2">
@@ -2255,10 +2347,10 @@
       <c r="B42" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="C42" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E42" s="2">
@@ -2287,10 +2379,10 @@
       <c r="B43" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D43" s="3" t="s">
+      <c r="C43" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E43" s="2">
@@ -2415,10 +2507,10 @@
       <c r="B47" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D47" s="3" t="s">
+      <c r="C47" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E47" s="2">
@@ -2447,10 +2539,10 @@
       <c r="B48" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D48" s="3" t="s">
+      <c r="C48" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E48" s="2">
@@ -2479,10 +2571,10 @@
       <c r="B49" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D49" s="3" t="s">
+      <c r="C49" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E49" s="2">
@@ -2511,10 +2603,10 @@
       <c r="B50" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D50" s="3" t="s">
+      <c r="C50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E50" s="2">
@@ -4719,10 +4811,10 @@
       <c r="B119" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C119" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D119" s="3" t="s">
+      <c r="C119" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D119" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E119" s="2"/>
@@ -4750,11 +4842,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4629F87-AE32-4135-AEE0-F396104DC0E9}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="13.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
@@ -4912,68 +5004,482 @@
         <v>2025</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>191</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>192</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="1" t="s">
-        <v>150</v>
-      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>12</v>
-      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2025</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D12" s="2">
         <v>45923</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E12" s="2">
         <v>45928</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
+    <row r="13" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45797</v>
+      </c>
+      <c r="E27" s="2">
+        <v>45802</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45664</v>
+      </c>
+      <c r="E29" s="2">
+        <v>45669</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B30" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C30" s="4" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
-      <c r="B10" s="1" t="s">
+    <row r="31" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="B31" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>169</v>
       </c>
+    </row>
+    <row r="32" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+    </row>
+    <row r="35" spans="1:4" s="1" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11028"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JH\code\badmintonAI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyh/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E81327-9C26-47A3-92C2-0EA0906ECB11}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEFA77-54A2-3147-B2BE-161FD02266D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="重大赛事" sheetId="1" r:id="rId1"/>
@@ -661,7 +661,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,21 +1014,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J119"/>
-  <sheetFormatPr defaultRowHeight="20.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="21"/>
   <cols>
-    <col min="1" max="1" width="7.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="15.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="48.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="48.1640625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24.5" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10">
       <c r="A2" s="1">
         <v>2026</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="A3" s="1">
         <v>2026</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="A4" s="1">
         <v>2026</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="A5" s="1">
         <v>2026</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="A6" s="1">
         <v>2026</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="A7" s="1">
         <v>2026</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="A8" s="1">
         <v>2026</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10">
       <c r="A9" s="1">
         <v>2026</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="A10" s="1">
         <v>2026</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10">
       <c r="A11" s="1">
         <v>2026</v>
       </c>
@@ -1380,7 +1380,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10">
       <c r="A12" s="1">
         <v>2026</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10">
       <c r="A13" s="1">
         <v>2026</v>
       </c>
@@ -1444,7 +1444,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10">
       <c r="A14" s="1">
         <v>2026</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="A15" s="1">
         <v>2026</v>
       </c>
@@ -1508,7 +1508,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="A16" s="1">
         <v>2026</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10">
       <c r="A17" s="1">
         <v>2026</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10">
       <c r="A18" s="1">
         <v>2026</v>
       </c>
@@ -1604,7 +1604,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10">
       <c r="A19" s="1">
         <v>2026</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10">
       <c r="A20" s="1">
         <v>2026</v>
       </c>
@@ -1668,7 +1668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10">
       <c r="A21" s="1">
         <v>2026</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10">
       <c r="A22" s="1">
         <v>2026</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10">
       <c r="A23" s="1">
         <v>2026</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10">
       <c r="A24" s="1">
         <v>2026</v>
       </c>
@@ -1796,7 +1796,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10">
       <c r="A25" s="1">
         <v>2026</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10">
       <c r="A26" s="1">
         <v>2026</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10">
       <c r="A27" s="1">
         <v>2025</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10">
       <c r="A28" s="1">
         <v>2025</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10">
       <c r="A29" s="1">
         <v>2025</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10">
       <c r="A30" s="1">
         <v>2025</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10">
       <c r="A31" s="1">
         <v>2025</v>
       </c>
@@ -2020,7 +2020,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10">
       <c r="A32" s="1">
         <v>2025</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10">
       <c r="A33" s="1">
         <v>2025</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10">
       <c r="A34" s="1">
         <v>2025</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10">
       <c r="A35" s="1">
         <v>2025</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10">
       <c r="A36" s="1">
         <v>2025</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10">
       <c r="A37" s="1">
         <v>2025</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10">
       <c r="A38" s="1">
         <v>2025</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10">
       <c r="A39" s="1">
         <v>2025</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10">
       <c r="A40" s="1">
         <v>2025</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10">
       <c r="A41" s="1">
         <v>2025</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10">
       <c r="A42" s="1">
         <v>2025</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10">
       <c r="A43" s="1">
         <v>2025</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10">
       <c r="A44" s="1">
         <v>2025</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10">
       <c r="A45" s="1">
         <v>2025</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10">
       <c r="A46" s="1">
         <v>2025</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10">
       <c r="A47" s="1">
         <v>2025</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10">
       <c r="A48" s="1">
         <v>2025</v>
       </c>
@@ -2564,7 +2564,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10">
       <c r="A49" s="1">
         <v>2025</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10">
       <c r="A50" s="1">
         <v>2025</v>
       </c>
@@ -2628,7 +2628,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10">
       <c r="A51" s="1">
         <v>2024</v>
       </c>
@@ -2660,17 +2660,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10">
       <c r="A52" s="1">
         <v>2024</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="C52" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E52" s="2">
@@ -2692,7 +2692,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10">
       <c r="A53" s="1">
         <v>2024</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10">
       <c r="A54" s="1">
         <v>2024</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10">
       <c r="A55" s="1">
         <v>2024</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10">
       <c r="A56" s="1">
         <v>2024</v>
       </c>
@@ -2820,7 +2820,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10">
       <c r="A57" s="1">
         <v>2024</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10">
       <c r="A58" s="1">
         <v>2024</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10">
       <c r="A59" s="1">
         <v>2024</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10">
       <c r="A60" s="1">
         <v>2024</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10">
       <c r="A61" s="1">
         <v>2024</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10">
       <c r="A62" s="1">
         <v>2024</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10">
       <c r="A63" s="1">
         <v>2024</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10">
       <c r="A64" s="1">
         <v>2024</v>
       </c>
@@ -3076,7 +3076,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10">
       <c r="A65" s="1">
         <v>2024</v>
       </c>
@@ -3108,7 +3108,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10">
       <c r="A66" s="1">
         <v>2024</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10">
       <c r="A67" s="1">
         <v>2024</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10">
       <c r="A68" s="1">
         <v>2024</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10">
       <c r="A69" s="1">
         <v>2024</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10">
       <c r="A70" s="1">
         <v>2024</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10">
       <c r="A71" s="1">
         <v>2024</v>
       </c>
@@ -3300,7 +3300,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10">
       <c r="A72" s="1">
         <v>2024</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10">
       <c r="A73" s="1">
         <v>2024</v>
       </c>
@@ -3364,7 +3364,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10">
       <c r="A74" s="1">
         <v>2024</v>
       </c>
@@ -3396,7 +3396,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10">
       <c r="A75" s="1">
         <v>2023</v>
       </c>
@@ -3428,7 +3428,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10">
       <c r="A76" s="1">
         <v>2023</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10">
       <c r="A77" s="1">
         <v>2023</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10">
       <c r="A78" s="1">
         <v>2023</v>
       </c>
@@ -3524,7 +3524,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10">
       <c r="A79" s="1">
         <v>2023</v>
       </c>
@@ -3556,7 +3556,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10">
       <c r="A80" s="1">
         <v>2023</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10">
       <c r="A81" s="1">
         <v>2023</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10">
       <c r="A82" s="1">
         <v>2023</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10">
       <c r="A83" s="1">
         <v>2023</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10">
       <c r="A84" s="1">
         <v>2023</v>
       </c>
@@ -3716,7 +3716,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10">
       <c r="A85" s="1">
         <v>2023</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10">
       <c r="A86" s="1">
         <v>2023</v>
       </c>
@@ -3780,7 +3780,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10">
       <c r="A87" s="1">
         <v>2023</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10">
       <c r="A88" s="1">
         <v>2023</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10">
       <c r="A89" s="1">
         <v>2023</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10">
       <c r="A90" s="1">
         <v>2023</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10">
       <c r="A91" s="1">
         <v>2023</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10">
       <c r="A92" s="1">
         <v>2023</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10">
       <c r="A93" s="1">
         <v>2023</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10">
       <c r="A94" s="1">
         <v>2023</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10">
       <c r="A95" s="1">
         <v>2023</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10">
       <c r="A96" s="1">
         <v>2023</v>
       </c>
@@ -4100,7 +4100,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10">
       <c r="A97" s="1">
         <v>2023</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10">
       <c r="A98" s="1">
         <v>2023</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10">
       <c r="A99" s="1">
         <v>2023</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10">
       <c r="A100" s="1">
         <v>2023</v>
       </c>
@@ -4228,7 +4228,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10">
       <c r="A101" s="1">
         <v>2022</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10">
       <c r="A102" s="1">
         <v>2022</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10">
       <c r="A103" s="1">
         <v>2022</v>
       </c>
@@ -4324,7 +4324,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10">
       <c r="A104" s="1">
         <v>2022</v>
       </c>
@@ -4356,7 +4356,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10">
       <c r="A105" s="1">
         <v>2022</v>
       </c>
@@ -4388,7 +4388,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10">
       <c r="A106" s="1">
         <v>2022</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10">
       <c r="A107" s="1">
         <v>2022</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10">
       <c r="A108" s="1">
         <v>2022</v>
       </c>
@@ -4484,7 +4484,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10">
       <c r="A109" s="1">
         <v>2022</v>
       </c>
@@ -4516,7 +4516,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10">
       <c r="A110" s="1">
         <v>2022</v>
       </c>
@@ -4548,7 +4548,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10">
       <c r="A111" s="1">
         <v>2022</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10">
       <c r="A112" s="1">
         <v>2022</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10">
       <c r="A113" s="1">
         <v>2022</v>
       </c>
@@ -4644,7 +4644,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10">
       <c r="A114" s="1">
         <v>2022</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10">
       <c r="A115" s="1">
         <v>2022</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10">
       <c r="A116" s="1">
         <v>2022</v>
       </c>
@@ -4740,7 +4740,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10">
       <c r="A117" s="1">
         <v>2022</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10">
       <c r="A118" s="1">
         <v>2022</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10">
       <c r="A119" s="1">
         <v>2021</v>
       </c>
@@ -4843,19 +4843,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4629F87-AE32-4135-AEE0-F396104DC0E9}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="21">
       <c r="A1" s="1" t="s">
         <v>163</v>
       </c>
@@ -4884,7 +4884,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="21">
       <c r="A2" s="1">
         <v>2026</v>
       </c>
@@ -4901,7 +4901,7 @@
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
     </row>
-    <row r="3" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="21">
       <c r="A3" s="1">
         <v>2026</v>
       </c>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="21">
       <c r="A4" s="1">
         <v>2026</v>
       </c>
@@ -4953,7 +4953,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="21">
       <c r="A5" s="1">
         <v>2026</v>
       </c>
@@ -4970,7 +4970,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="21">
       <c r="A6" s="1">
         <v>2026</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="21">
       <c r="A7" s="1">
         <v>2025</v>
       </c>
@@ -5016,7 +5016,7 @@
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
     </row>
-    <row r="8" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="21">
       <c r="A8" s="1">
         <v>2025</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="21">
       <c r="A9" s="1">
         <v>2025</v>
       </c>
@@ -5056,7 +5056,7 @@
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
     </row>
-    <row r="10" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="21">
       <c r="A10" s="1">
         <v>2025</v>
       </c>
@@ -5073,7 +5073,7 @@
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
     </row>
-    <row r="11" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="21">
       <c r="A11" s="1">
         <v>2025</v>
       </c>
@@ -5090,7 +5090,7 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="21">
       <c r="A12" s="1">
         <v>2025</v>
       </c>
@@ -5119,7 +5119,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="21">
       <c r="A13" s="1">
         <v>2025</v>
       </c>
@@ -5136,7 +5136,7 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="21">
       <c r="A14" s="1">
         <v>2025</v>
       </c>
@@ -5153,7 +5153,7 @@
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
-    <row r="15" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="21">
       <c r="A15" s="1">
         <v>2025</v>
       </c>
@@ -5170,7 +5170,7 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="21">
       <c r="A16" s="1">
         <v>2025</v>
       </c>
@@ -5187,7 +5187,7 @@
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
     </row>
-    <row r="17" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="21">
       <c r="A17" s="1">
         <v>2025</v>
       </c>
@@ -5204,7 +5204,7 @@
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
     </row>
-    <row r="18" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="21">
       <c r="A18" s="1">
         <v>2025</v>
       </c>
@@ -5221,7 +5221,7 @@
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
     </row>
-    <row r="19" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="21">
       <c r="A19" s="1">
         <v>2025</v>
       </c>
@@ -5238,7 +5238,7 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
-    <row r="20" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="21">
       <c r="A20" s="1">
         <v>2025</v>
       </c>
@@ -5255,7 +5255,7 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
     </row>
-    <row r="21" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="21">
       <c r="A21" s="1">
         <v>2025</v>
       </c>
@@ -5272,7 +5272,7 @@
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="21">
       <c r="A22" s="1">
         <v>2025</v>
       </c>
@@ -5289,7 +5289,7 @@
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
-    <row r="23" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="21">
       <c r="A23" s="1">
         <v>2025</v>
       </c>
@@ -5306,7 +5306,7 @@
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
-    <row r="24" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="21">
       <c r="A24" s="1">
         <v>2025</v>
       </c>
@@ -5323,7 +5323,7 @@
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
     </row>
-    <row r="25" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="21">
       <c r="A25" s="1">
         <v>2025</v>
       </c>
@@ -5340,7 +5340,7 @@
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
     </row>
-    <row r="26" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="21">
       <c r="A26" s="1">
         <v>2025</v>
       </c>
@@ -5357,7 +5357,7 @@
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
     </row>
-    <row r="27" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="21">
       <c r="A27" s="1">
         <v>2025</v>
       </c>
@@ -5386,7 +5386,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="21">
       <c r="A28" s="1">
         <v>2025</v>
       </c>
@@ -5403,7 +5403,7 @@
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
     </row>
-    <row r="29" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="21">
       <c r="A29" s="1">
         <v>2025</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="21">
       <c r="B30" s="1" t="s">
         <v>164</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="21">
       <c r="B31" s="1" t="s">
         <v>168</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="21">
       <c r="A32" s="1">
         <v>2021</v>
       </c>
@@ -5473,11 +5473,11 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" ht="21">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
     </row>
-    <row r="35" spans="1:4" s="1" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" s="1" customFormat="1" ht="21">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyh/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyh/Desktop/____MyWork/016_ badminton_download/badmintonAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFEFA77-54A2-3147-B2BE-161FD02266D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE8DCD4-82EC-4844-BFA6-F2E4B5C32B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2635,10 +2635,10 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D51" s="3" t="s">
+      <c r="C51" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E51" s="2">
@@ -2699,10 +2699,10 @@
       <c r="B53" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C53" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D53" s="3" t="s">
+      <c r="C53" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E53" s="2">
@@ -2731,10 +2731,10 @@
       <c r="B54" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D54" s="3" t="s">
+      <c r="C54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E54" s="2">
@@ -2763,10 +2763,10 @@
       <c r="B55" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D55" s="3" t="s">
+      <c r="C55" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E55" s="2">
@@ -2795,10 +2795,10 @@
       <c r="B56" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D56" s="3" t="s">
+      <c r="C56" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E56" s="2">
@@ -2827,10 +2827,10 @@
       <c r="B57" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C57" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D57" s="3" t="s">
+      <c r="C57" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E57" s="2">
@@ -2859,10 +2859,10 @@
       <c r="B58" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D58" s="3" t="s">
+      <c r="C58" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E58" s="2">
@@ -2891,10 +2891,10 @@
       <c r="B59" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="C59" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E59" s="2">
@@ -2955,10 +2955,10 @@
       <c r="B61" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D61" s="3" t="s">
+      <c r="C61" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E61" s="2">
@@ -2987,10 +2987,10 @@
       <c r="B62" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D62" s="3" t="s">
+      <c r="C62" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E62" s="2">
@@ -3019,10 +3019,10 @@
       <c r="B63" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D63" s="3" t="s">
+      <c r="C63" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E63" s="2">
@@ -3051,10 +3051,10 @@
       <c r="B64" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C64" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D64" s="3" t="s">
+      <c r="C64" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E64" s="2">
@@ -3083,10 +3083,10 @@
       <c r="B65" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="C65" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E65" s="2">
@@ -3243,10 +3243,10 @@
       <c r="B70" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="C70" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E70" s="2">

--- a/matches.xlsx
+++ b/matches.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyh/Desktop/____MyWork/016_ badminton_download/badmintonAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFE8DCD4-82EC-4844-BFA6-F2E4B5C32B41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34158469-A3EA-EF48-A397-075726CB8FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="16160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="重大赛事" sheetId="1" r:id="rId1"/>
@@ -3403,10 +3403,10 @@
       <c r="B75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="C75" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E75" s="2">
@@ -3467,10 +3467,10 @@
       <c r="B77" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D77" s="3" t="s">
+      <c r="C77" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E77" s="2">
@@ -3595,10 +3595,10 @@
       <c r="B81" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C81" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D81" s="3" t="s">
+      <c r="C81" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E81" s="2">
@@ -3659,10 +3659,10 @@
       <c r="B83" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C83" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D83" s="3" t="s">
+      <c r="C83" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E83" s="2">
@@ -3691,10 +3691,10 @@
       <c r="B84" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C84" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D84" s="3" t="s">
+      <c r="C84" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E84" s="2">
@@ -3755,10 +3755,10 @@
       <c r="B86" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D86" s="3" t="s">
+      <c r="C86" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D86" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E86" s="2">
@@ -3819,10 +3819,10 @@
       <c r="B88" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D88" s="3" t="s">
+      <c r="C88" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E88" s="2">
@@ -3851,10 +3851,10 @@
       <c r="B89" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C89" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D89" s="3" t="s">
+      <c r="C89" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E89" s="2">
@@ -3915,10 +3915,10 @@
       <c r="B91" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C91" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D91" s="3" t="s">
+      <c r="C91" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D91" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E91" s="2">
@@ -3947,10 +3947,10 @@
       <c r="B92" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D92" s="3" t="s">
+      <c r="C92" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D92" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E92" s="2">
@@ -3979,10 +3979,10 @@
       <c r="B93" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C93" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D93" s="3" t="s">
+      <c r="C93" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D93" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E93" s="2">
@@ -4011,10 +4011,10 @@
       <c r="B94" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C94" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D94" s="3" t="s">
+      <c r="C94" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E94" s="2">
@@ -4107,10 +4107,10 @@
       <c r="B97" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C97" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D97" s="3" t="s">
+      <c r="C97" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D97" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E97" s="2">
@@ -4171,10 +4171,10 @@
       <c r="B99" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C99" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D99" s="3" t="s">
+      <c r="C99" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D99" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E99" s="2">
@@ -4203,10 +4203,10 @@
       <c r="B100" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C100" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D100" s="3" t="s">
+      <c r="C100" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D100" s="4" t="s">
         <v>148</v>
       </c>
       <c r="E100" s="2">
